--- a/assets/docs/relatorios/fundamentos-gestao-publica-2026-05/turma 1/participantes.xlsx
+++ b/assets/docs/relatorios/fundamentos-gestao-publica-2026-05/turma 1/participantes.xlsx
@@ -35,12 +35,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -449,19 +445,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Polyana Parreiras</v>
+        <v>Adriana Cristiene Demétrio</v>
       </c>
       <c r="B2" t="str">
-        <v>polyana.parreiras@pedroleopoldo.mg.gov.br</v>
+        <v>adriana.demetrio@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C2" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D2" t="str">
-        <v>supervisora</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E2" t="str">
-        <v>8753</v>
+        <v>9257</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -479,10 +475,10 @@
         <v>Sim</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-05-11 14:10:48</v>
+        <v>2026-05-11 15:35:16</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-05-14 15:11:22</v>
+        <v>2026-05-14 15:11:41</v>
       </c>
       <c r="M2" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -490,19 +486,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Renata dos Santos Nestor</v>
+        <v>Adriana Paçanha Batista</v>
       </c>
       <c r="B3" t="str">
-        <v>renata.nestor@pedroleopoldo.mg.gov.br</v>
+        <v>adriana.batista@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C3" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D3" t="str">
-        <v>ASSISTENTE ADMINISTRATIVO</v>
+        <v>DCA-3 SGF30000</v>
       </c>
       <c r="E3" t="str">
-        <v>08307</v>
+        <v>36104</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -520,10 +516,10 @@
         <v>Sim</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-05-11 14:10:52</v>
+        <v>2026-05-12 10:43:41</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-05-14 15:11:24</v>
+        <v>2026-05-14 15:11:58</v>
       </c>
       <c r="M3" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -531,19 +527,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Patricia Pereira de Araujo Fernandes</v>
+        <v>Adriane Marques</v>
       </c>
       <c r="B4" t="str">
-        <v>paty2582@gmail.com</v>
+        <v>adrianemarquezcursos@gmail.com</v>
       </c>
       <c r="C4" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D4" t="str">
-        <v>Assistente Administrativo</v>
+        <v>DCA-1</v>
       </c>
       <c r="E4" t="str">
-        <v>8305</v>
+        <v>35078</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -561,10 +557,10 @@
         <v>Sim</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-05-11 14:13:47</v>
+        <v>2026-05-11 16:13:50</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-05-14 15:11:19</v>
+        <v>2026-05-14 15:11:37</v>
       </c>
       <c r="M4" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -572,19 +568,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pedro Alcantara</v>
+        <v>Alexandre Thadeu Clemente Bassouto</v>
       </c>
       <c r="B5" t="str">
-        <v>pedro.alcantara@pedroleopoldo.mg.gov.br</v>
+        <v>alexandre@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C5" t="str">
-        <v>Secretaria Municipal de Saúde</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D5" t="str">
-        <v>Diretora</v>
+        <v>Analista de Sistemas e Redes</v>
       </c>
       <c r="E5" t="str">
-        <v>35043</v>
+        <v>8076</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -602,10 +598,10 @@
         <v>Sim</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-05-11 14:17:53</v>
+        <v>2026-05-13 11:15:13</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-05-14 15:13:25</v>
+        <v>2026-05-14 15:11:36</v>
       </c>
       <c r="M5" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -613,19 +609,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Luziana Lima</v>
+        <v>Ana de Jesus</v>
       </c>
       <c r="B6" t="str">
-        <v>luzianalimacampos@gmail.com</v>
+        <v>ana.jesus@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C6" t="str">
-        <v>Secretaria Municipal de Saúde</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D6" t="str">
-        <v>Assistente administrativo</v>
+        <v>ANALISTA ADMINISTRATIVO</v>
       </c>
       <c r="E6" t="str">
-        <v>34984</v>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -634,7 +630,7 @@
         <v>Não</v>
       </c>
       <c r="H6" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I6" t="str">
         <v>Não</v>
@@ -643,10 +639,10 @@
         <v>Não</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-05-11 14:20:23</v>
+        <v>2026-05-13 10:25:47</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>2026-05-14 15:12:05</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -654,19 +650,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Monica Cruz Vieira</v>
+        <v>Andréa Mara da Cruz Rocha</v>
       </c>
       <c r="B7" t="str">
-        <v>monica.vieira@pedroleopoldo.mg.gov.br</v>
+        <v>andrea.rocha@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C7" t="str">
-        <v>Controladoria Geral do Município</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D7" t="str">
-        <v>Administração</v>
+        <v>Assessor</v>
       </c>
       <c r="E7" t="str">
-        <v>0</v>
+        <v>35006</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -684,10 +680,10 @@
         <v>Sim</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-05-11 14:22:36</v>
+        <v>2026-05-11 15:41:38</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-05-14 15:13:10</v>
+        <v>2026-05-14 15:11:02</v>
       </c>
       <c r="M7" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -695,19 +691,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Maria Inêsclemente Bassouto Estevam</v>
+        <v>Arthur Serafim</v>
       </c>
       <c r="B8" t="str">
-        <v>maria.estevam@pedroleopoldo.mg.gov.br</v>
+        <v>arthur.serafim@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C8" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D8" t="str">
-        <v>Gerente de Saúde Ocupacional</v>
+        <v>Gerente de contratos e convênios públicos</v>
       </c>
       <c r="E8" t="str">
-        <v>8295</v>
+        <v>36010</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -725,10 +721,10 @@
         <v>Sim</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-05-11 14:23:50</v>
+        <v>2026-05-13 13:27:06</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-05-14 15:11:15</v>
+        <v>2026-05-14 15:10:33</v>
       </c>
       <c r="M8" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -736,19 +732,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Adriana Cristiene Demétrio</v>
+        <v>Aurelio Collor Duarte Goncalves Nunes</v>
       </c>
       <c r="B9" t="str">
-        <v>adriana.demetrio@pedroleopoldo.mg.gov.br</v>
+        <v>aurelio.nunes@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C9" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D9" t="str">
-        <v>Assistente Administrativo</v>
+        <v>Supervisor Cibersegurança</v>
       </c>
       <c r="E9" t="str">
-        <v>9257</v>
+        <v>36118</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -766,10 +762,10 @@
         <v>Sim</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-05-11 15:35:16</v>
+        <v>2026-05-13 16:28:54</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-05-14 15:11:41</v>
+        <v>2026-05-14 15:11:35</v>
       </c>
       <c r="M9" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -777,19 +773,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Andréa Mara da Cruz Rocha</v>
+        <v>Breno Henrique da Silva Ramalho</v>
       </c>
       <c r="B10" t="str">
-        <v>andrea.rocha@pedroleopoldo.mg.gov.br</v>
+        <v>breno.ramalho@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C10" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D10" t="str">
-        <v>Assessor</v>
+        <v>Estagio Pós Graduação</v>
       </c>
       <c r="E10" t="str">
-        <v>35006</v>
+        <v>12891553640</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -807,10 +803,10 @@
         <v>Sim</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-05-11 15:41:38</v>
+        <v>2026-05-12 11:03:00</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-05-14 15:11:02</v>
+        <v>2026-05-14 15:12:10</v>
       </c>
       <c r="M10" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -818,19 +814,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Adriane Marques</v>
+        <v>Diego Domiciano</v>
       </c>
       <c r="B11" t="str">
-        <v>adrianemarquezcursos@gmail.com</v>
+        <v>diegoskywalker88@gmail.com</v>
       </c>
       <c r="C11" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D11" t="str">
-        <v>DCA-1</v>
+        <v>DCA-4</v>
       </c>
       <c r="E11" t="str">
-        <v>35078</v>
+        <v>170787</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -848,10 +844,10 @@
         <v>Sim</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-05-11 16:13:50</v>
+        <v>2026-05-12 10:42:11</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-05-14 15:11:37</v>
+        <v>2026-05-14 15:10:03</v>
       </c>
       <c r="M11" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -859,19 +855,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Tassia Junqueira</v>
+        <v>Fabiana Cristina da Silva</v>
       </c>
       <c r="B12" t="str">
-        <v>tassia.junqueira@pedroleopoldo.mg.gov.br</v>
+        <v>fabiana.silva@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C12" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D12" t="str">
-        <v>GERENTE</v>
+        <v>Gerente de cargos, carreira e desenvolvimento</v>
       </c>
       <c r="E12" t="str">
-        <v>34996</v>
+        <v>10013</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -889,30 +885,30 @@
         <v>Sim</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-05-11 16:49:50</v>
+        <v>2026-05-12 15:34:11</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-05-14 15:11:27</v>
+        <v>2026-05-14 15:12:20</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-26 09:00:00</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Olga Arruda Cruz</v>
+        <v>Flavio Damaso</v>
       </c>
       <c r="B13" t="str">
-        <v>olga_arruda@hotmail.com</v>
+        <v>flavio.damaso@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C13" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D13" t="str">
-        <v>Supervisora</v>
+        <v>Diretor de Compras Públicas</v>
       </c>
       <c r="E13" t="str">
-        <v>33291</v>
+        <v>05994</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -924,16 +920,16 @@
         <v>Sim</v>
       </c>
       <c r="I13" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="J13" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-05-11 16:58:37</v>
+        <v>2026-05-13 11:17:18</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-05-14 15:10:13</v>
+        <v>2026-05-14 15:12:20</v>
       </c>
       <c r="M13" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -941,40 +937,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Patrícia Duarte Costa Pereira</v>
+        <v>Ilda Graciele Moreira Leite</v>
       </c>
       <c r="B14" t="str">
-        <v>patricia.pereira@pedroleopoldo.mg.gov.br</v>
+        <v>graciele.leite@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C14" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D14" t="str">
-        <v>Gerente</v>
+        <v>SUPERVISÃO DE ORDEM DE SERVIÇOS</v>
       </c>
       <c r="E14" t="str">
-        <v>34985</v>
+        <v>35048</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H14" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I14" t="str">
         <v>Sim</v>
       </c>
       <c r="J14" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-05-11 18:17:32</v>
+        <v>2026-05-13 13:32:22</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-05-14 15:13:17</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -982,81 +978,81 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Marcia Alves</v>
+        <v>Italo Samuel Peçanha Pinto</v>
       </c>
       <c r="B15" t="str">
-        <v>Libaniacassia@hotmail.com</v>
+        <v>italo.pecanha@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C15" t="str">
-        <v>Secretaria Municipal de Governo</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D15" t="str">
-        <v>coordenadora de projetos</v>
+        <v>Supervisor de Redes de Computadores</v>
       </c>
       <c r="E15" t="str">
-        <v>0</v>
+        <v>36116</v>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H15" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I15" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="J15" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-05-11 19:19:39</v>
+        <v>2026-05-13 19:09:49</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>2026-05-14 15:11:07</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-05-26 09:00:00</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Leandro Ramos Macedo</v>
+        <v>Kelen Lourenço Silva Oliveira</v>
       </c>
       <c r="B16" t="str">
-        <v>leandro.macedo@pedroleopoldo.mg.gov.br</v>
+        <v>kelen.oliveira@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C16" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D16" t="str">
-        <v>Coordenador de Patrimônio e Logística</v>
+        <v>Coordenador de Assessoramento</v>
       </c>
       <c r="E16" t="str">
-        <v>36494</v>
+        <v>8113</v>
       </c>
       <c r="F16" t="str">
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H16" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I16" t="str">
         <v>Sim</v>
       </c>
       <c r="J16" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-05-12 09:12:40</v>
+        <v>2026-05-14 09:06:56</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-05-14 15:12:50</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1064,60 +1060,60 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Rodrigo Calazans</v>
+        <v>Leandro Ramos Macedo</v>
       </c>
       <c r="B17" t="str">
-        <v>rodrigo.diogo@pedroleopoldo.mg.gov.br</v>
+        <v>leandro.macedo@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C17" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D17" t="str">
-        <v>Coordenador</v>
+        <v>Coordenador de Patrimônio e Logística</v>
       </c>
       <c r="E17" t="str">
-        <v>36006</v>
+        <v>36494</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H17" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I17" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="J17" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-05-12 10:38:20</v>
+        <v>2026-05-12 09:12:40</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>2026-05-14 15:12:50</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2026-05-26 09:00:00</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Diego Domiciano</v>
+        <v>Libânia Alves</v>
       </c>
       <c r="B18" t="str">
-        <v>diegoskywalker88@gmail.com</v>
+        <v>libaniacassia@hotmail.com</v>
       </c>
       <c r="C18" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Governo</v>
       </c>
       <c r="D18" t="str">
-        <v>DCA-4</v>
+        <v>Assessoria</v>
       </c>
       <c r="E18" t="str">
-        <v>170787</v>
+        <v>000001</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1135,10 +1131,10 @@
         <v>Sim</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-05-12 10:42:11</v>
+        <v>2026-05-12 18:46:22</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-05-14 15:10:03</v>
+        <v>2026-05-14 15:11:10</v>
       </c>
       <c r="M18" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1146,19 +1142,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Adriana Paçanha Batista</v>
+        <v>Lucelho Cristiano Vieira da Silva</v>
       </c>
       <c r="B19" t="str">
-        <v>adriana.batista@pedroleopoldo.mg.gov.br</v>
+        <v>lucelho.silva@elkys.com.br</v>
       </c>
       <c r="C19" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D19" t="str">
-        <v>DCA-3 SGF30000</v>
+        <v>Assessor em soluções Tecnologicas</v>
       </c>
       <c r="E19" t="str">
-        <v>36104</v>
+        <v>3583-8</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1176,10 +1172,10 @@
         <v>Sim</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-05-12 10:43:41</v>
+        <v>2026-05-13 15:27:09</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-05-14 15:11:58</v>
+        <v>2026-05-14 15:11:11</v>
       </c>
       <c r="M19" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1187,60 +1183,60 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Breno Henrique da Silva Ramalho</v>
+        <v>Luziana Lima</v>
       </c>
       <c r="B20" t="str">
-        <v>breno.ramalho@pedroleopoldo.mg.gov.br</v>
+        <v>luzianalimacampos@gmail.com</v>
       </c>
       <c r="C20" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Saúde</v>
       </c>
       <c r="D20" t="str">
-        <v>Estagio Pós Graduação</v>
+        <v>Assistente administrativo</v>
       </c>
       <c r="E20" t="str">
-        <v>12891553640</v>
+        <v>34984</v>
       </c>
       <c r="F20" t="str">
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H20" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I20" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="J20" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-05-12 11:03:00</v>
+        <v>2026-05-11 14:20:23</v>
       </c>
       <c r="L20" t="str">
-        <v>2026-05-14 15:12:10</v>
+        <v/>
       </c>
       <c r="M20" t="str">
-        <v>2026-05-26 09:00:00</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Samu Nasser</v>
+        <v>Makerly Maia Toledo</v>
       </c>
       <c r="B21" t="str">
-        <v>samuel.nasta@pedroleopoldo.mg.gov.br</v>
+        <v>makerlymaiatoledo@gmail.com</v>
       </c>
       <c r="C21" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D21" t="str">
-        <v>Desenvolvedor full stack</v>
+        <v>Diretor</v>
       </c>
       <c r="E21" t="str">
-        <v>31068</v>
+        <v>3499-5</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1258,10 +1254,10 @@
         <v>Sim</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-05-12 12:55:51</v>
+        <v>2026-05-13 10:21:04</v>
       </c>
       <c r="L21" t="str">
-        <v>2026-05-14 15:11:27</v>
+        <v>2026-05-14 15:11:13</v>
       </c>
       <c r="M21" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1269,19 +1265,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Fabiana Cristina da Silva</v>
+        <v>Marcia Alves</v>
       </c>
       <c r="B22" t="str">
-        <v>fabiana.silva@pedroleopoldo.mg.gov.br</v>
+        <v>Libaniacassia@hotmail.com</v>
       </c>
       <c r="C22" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Governo</v>
       </c>
       <c r="D22" t="str">
-        <v>Gerente de cargos, carreira e desenvolvimento</v>
+        <v>coordenadora de projetos</v>
       </c>
       <c r="E22" t="str">
-        <v>10013</v>
+        <v>0</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1290,7 +1286,7 @@
         <v>Não</v>
       </c>
       <c r="H22" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I22" t="str">
         <v>Não</v>
@@ -1299,10 +1295,10 @@
         <v>Não</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-05-12 15:34:11</v>
+        <v>2026-05-11 19:19:39</v>
       </c>
       <c r="L22" t="str">
-        <v>2026-05-14 15:12:20</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1310,60 +1306,60 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Poliana Almeida Braga</v>
+        <v>Maria Inêsclemente Bassouto Estevam</v>
       </c>
       <c r="B23" t="str">
-        <v>poliana.braga@pedroleopoldo.mg.gov.br</v>
+        <v>maria.estevam@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C23" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D23" t="str">
-        <v>Assistente Administrativo</v>
+        <v>Gerente de Saúde Ocupacional</v>
       </c>
       <c r="E23" t="str">
-        <v>10069</v>
+        <v>8295</v>
       </c>
       <c r="F23" t="str">
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H23" t="str">
         <v>Sim</v>
       </c>
       <c r="I23" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="J23" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-05-12 16:52:36</v>
+        <v>2026-05-11 14:23:50</v>
       </c>
       <c r="L23" t="str">
-        <v>2026-05-14 15:13:30</v>
+        <v>2026-05-14 15:11:15</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>2026-05-26 09:00:00</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Libânia Alves</v>
+        <v>Michele Oliveira Xavier Corradi</v>
       </c>
       <c r="B24" t="str">
-        <v>libaniacassia@hotmail.com</v>
+        <v>michele.corradi@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C24" t="str">
-        <v>Secretaria Municipal de Governo</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D24" t="str">
-        <v>Assessoria</v>
+        <v>Supervisor em Planejamento</v>
       </c>
       <c r="E24" t="str">
-        <v>000001</v>
+        <v>35982</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1381,10 +1377,10 @@
         <v>Sim</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-05-12 18:46:22</v>
+        <v>2026-05-13 19:16:39</v>
       </c>
       <c r="L24" t="str">
-        <v>2026-05-14 15:11:10</v>
+        <v>2026-05-14 15:10:49</v>
       </c>
       <c r="M24" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1392,19 +1388,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Priscila Malaquias</v>
+        <v>Miriam Mara da Silva Ramalho</v>
       </c>
       <c r="B25" t="str">
-        <v>priscila.malaquias@pedroleopoldo.mg.gov.br</v>
+        <v>miriam.1969@hotmail.com</v>
       </c>
       <c r="C25" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D25" t="str">
-        <v>Analista Administrativo</v>
+        <v>Contabilidade</v>
       </c>
       <c r="E25" t="str">
-        <v>36839</v>
+        <v>70426368649</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1422,10 +1418,10 @@
         <v>Sim</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-05-13 08:57:59</v>
+        <v>2026-05-13 19:29:47</v>
       </c>
       <c r="L25" t="str">
-        <v>2026-05-14 15:11:24</v>
+        <v>2026-05-14 15:10:42</v>
       </c>
       <c r="M25" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1433,19 +1429,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Thais Aparecida</v>
+        <v>Monica Cruz Vieira</v>
       </c>
       <c r="B26" t="str">
-        <v>thaisaparecidamtz@hotmail.com</v>
+        <v>monica.vieira@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C26" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Controladoria Geral do Município</v>
       </c>
       <c r="D26" t="str">
-        <v>Assistente Administrativo</v>
+        <v>Administração</v>
       </c>
       <c r="E26" t="str">
-        <v>36840</v>
+        <v>0</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1463,10 +1459,10 @@
         <v>Sim</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-05-13 08:58:54</v>
+        <v>2026-05-11 14:22:36</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-05-14 15:10:56</v>
+        <v>2026-05-14 15:13:10</v>
       </c>
       <c r="M26" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1474,40 +1470,40 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Makerly Maia Toledo</v>
+        <v>Olga Arruda Cruz</v>
       </c>
       <c r="B27" t="str">
-        <v>makerlymaiatoledo@gmail.com</v>
+        <v>olga_arruda@hotmail.com</v>
       </c>
       <c r="C27" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D27" t="str">
-        <v>Diretor</v>
+        <v>Supervisora</v>
       </c>
       <c r="E27" t="str">
-        <v>3499-5</v>
+        <v>33291</v>
       </c>
       <c r="F27" t="str">
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H27" t="str">
         <v>Sim</v>
       </c>
       <c r="I27" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="J27" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-05-13 10:21:04</v>
+        <v>2026-05-11 16:58:37</v>
       </c>
       <c r="L27" t="str">
-        <v>2026-05-14 15:11:13</v>
+        <v>2026-05-14 15:10:13</v>
       </c>
       <c r="M27" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1515,60 +1511,60 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ana de Jesus</v>
+        <v>Patrícia Duarte Costa Pereira</v>
       </c>
       <c r="B28" t="str">
-        <v>ana.jesus@pedroleopoldo.mg.gov.br</v>
+        <v>patricia.pereira@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C28" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D28" t="str">
-        <v>ANALISTA ADMINISTRATIVO</v>
+        <v>Gerente</v>
       </c>
       <c r="E28" t="str">
-        <v>0</v>
+        <v>34985</v>
       </c>
       <c r="F28" t="str">
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H28" t="str">
         <v>Sim</v>
       </c>
       <c r="I28" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="J28" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-05-13 10:25:47</v>
+        <v>2026-05-11 18:17:32</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-05-14 15:12:05</v>
+        <v>2026-05-14 15:13:17</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>2026-05-26 09:00:00</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Alexandre Thadeu Clemente Bassouto</v>
+        <v>Patricia Pereira de Araujo Fernandes</v>
       </c>
       <c r="B29" t="str">
-        <v>alexandre@pedroleopoldo.mg.gov.br</v>
+        <v>paty2582@gmail.com</v>
       </c>
       <c r="C29" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D29" t="str">
-        <v>Analista de Sistemas e Redes</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E29" t="str">
-        <v>8076</v>
+        <v>8305</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1586,10 +1582,10 @@
         <v>Sim</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-05-13 11:15:13</v>
+        <v>2026-05-11 14:13:47</v>
       </c>
       <c r="L29" t="str">
-        <v>2026-05-14 15:11:36</v>
+        <v>2026-05-14 15:11:19</v>
       </c>
       <c r="M29" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1597,19 +1593,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Flavio Damaso</v>
+        <v>Pedro Alcantara</v>
       </c>
       <c r="B30" t="str">
-        <v>flavio.damaso@pedroleopoldo.mg.gov.br</v>
+        <v>pedro.alcantara@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C30" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Saúde</v>
       </c>
       <c r="D30" t="str">
-        <v>Diretor de Compras Públicas</v>
+        <v>Diretora</v>
       </c>
       <c r="E30" t="str">
-        <v>05994</v>
+        <v>35043</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1627,10 +1623,10 @@
         <v>Sim</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-05-13 11:17:18</v>
+        <v>2026-05-11 14:17:53</v>
       </c>
       <c r="L30" t="str">
-        <v>2026-05-14 15:12:20</v>
+        <v>2026-05-14 15:13:25</v>
       </c>
       <c r="M30" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1638,60 +1634,60 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Victor Hugo Pereira Reis</v>
+        <v>Poliana Almeida Braga</v>
       </c>
       <c r="B31" t="str">
-        <v>victor.reis@pedroleopoldo.mg.gov.br</v>
+        <v>poliana.braga@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C31" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D31" t="str">
-        <v>Gerente de Infraestrutura de TIC</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E31" t="str">
-        <v>9076</v>
+        <v>10069</v>
       </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H31" t="str">
         <v>Sim</v>
       </c>
       <c r="I31" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="J31" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-05-13 11:32:06</v>
+        <v>2026-05-12 16:52:36</v>
       </c>
       <c r="L31" t="str">
-        <v>2026-05-14 15:10:07</v>
+        <v>2026-05-14 15:13:30</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-05-26 09:00:00</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Arthur Serafim</v>
+        <v>Polyana Parreiras</v>
       </c>
       <c r="B32" t="str">
-        <v>arthur.serafim@pedroleopoldo.mg.gov.br</v>
+        <v>polyana.parreiras@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C32" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D32" t="str">
-        <v>Gerente de contratos e convênios públicos</v>
+        <v>supervisora</v>
       </c>
       <c r="E32" t="str">
-        <v>36010</v>
+        <v>8753</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1709,10 +1705,10 @@
         <v>Sim</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-05-13 13:27:06</v>
+        <v>2026-05-11 14:10:48</v>
       </c>
       <c r="L32" t="str">
-        <v>2026-05-14 15:10:33</v>
+        <v>2026-05-14 15:11:22</v>
       </c>
       <c r="M32" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1720,40 +1716,40 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ilda Graciele Moreira Leite</v>
+        <v>Priscila Malaquias</v>
       </c>
       <c r="B33" t="str">
-        <v>graciele.leite@pedroleopoldo.mg.gov.br</v>
+        <v>priscila.malaquias@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C33" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D33" t="str">
-        <v>SUPERVISÃO DE ORDEM DE SERVIÇOS</v>
+        <v>Analista Administrativo</v>
       </c>
       <c r="E33" t="str">
-        <v>35048</v>
+        <v>36839</v>
       </c>
       <c r="F33" t="str">
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H33" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I33" t="str">
         <v>Sim</v>
       </c>
       <c r="J33" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-05-13 13:32:22</v>
+        <v>2026-05-13 08:57:59</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>2026-05-14 15:11:24</v>
       </c>
       <c r="M33" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1761,19 +1757,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lucelho Cristiano Vieira da Silva</v>
+        <v>Renata dos Santos Nestor</v>
       </c>
       <c r="B34" t="str">
-        <v>lucelho.silva@elkys.com.br</v>
+        <v>renata.nestor@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C34" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D34" t="str">
-        <v>Assessor em soluções Tecnologicas</v>
+        <v>ASSISTENTE ADMINISTRATIVO</v>
       </c>
       <c r="E34" t="str">
-        <v>3583-8</v>
+        <v>08307</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1791,10 +1787,10 @@
         <v>Sim</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-05-13 15:27:09</v>
+        <v>2026-05-11 14:10:52</v>
       </c>
       <c r="L34" t="str">
-        <v>2026-05-14 15:11:11</v>
+        <v>2026-05-14 15:11:24</v>
       </c>
       <c r="M34" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1802,60 +1798,60 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Aurelio Collor Duarte Goncalves Nunes</v>
+        <v>Rodrigo Calazans</v>
       </c>
       <c r="B35" t="str">
-        <v>aurelio.nunes@pedroleopoldo.mg.gov.br</v>
+        <v>rodrigo.diogo@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C35" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D35" t="str">
-        <v>Supervisor Cibersegurança</v>
+        <v>Coordenador</v>
       </c>
       <c r="E35" t="str">
-        <v>36118</v>
+        <v>36006</v>
       </c>
       <c r="F35" t="str">
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H35" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I35" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="J35" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-05-13 16:28:54</v>
+        <v>2026-05-12 10:38:20</v>
       </c>
       <c r="L35" t="str">
-        <v>2026-05-14 15:11:35</v>
+        <v/>
       </c>
       <c r="M35" t="str">
-        <v>2026-05-26 09:00:00</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Italo Samuel Peçanha Pinto</v>
+        <v>Samu Nasser</v>
       </c>
       <c r="B36" t="str">
-        <v>italo.pecanha@pedroleopoldo.mg.gov.br</v>
+        <v>samuel.nasta@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C36" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D36" t="str">
-        <v>Supervisor de Redes de Computadores</v>
+        <v>Desenvolvedor full stack</v>
       </c>
       <c r="E36" t="str">
-        <v>36116</v>
+        <v>31068</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -1873,10 +1869,10 @@
         <v>Sim</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-05-13 19:09:49</v>
+        <v>2026-05-12 12:55:51</v>
       </c>
       <c r="L36" t="str">
-        <v>2026-05-14 15:11:07</v>
+        <v>2026-05-14 15:11:27</v>
       </c>
       <c r="M36" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1884,19 +1880,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Michele Oliveira Xavier Corradi</v>
+        <v>Tassia Junqueira</v>
       </c>
       <c r="B37" t="str">
-        <v>michele.corradi@pedroleopoldo.mg.gov.br</v>
+        <v>tassia.junqueira@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C37" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D37" t="str">
-        <v>Supervisor em Planejamento</v>
+        <v>GERENTE</v>
       </c>
       <c r="E37" t="str">
-        <v>35982</v>
+        <v>34996</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -1914,10 +1910,10 @@
         <v>Sim</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-05-13 19:16:39</v>
+        <v>2026-05-11 16:49:50</v>
       </c>
       <c r="L37" t="str">
-        <v>2026-05-14 15:10:49</v>
+        <v>2026-05-14 15:11:27</v>
       </c>
       <c r="M37" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1925,19 +1921,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Miriam Mara da Silva Ramalho</v>
+        <v>Thais Aparecida</v>
       </c>
       <c r="B38" t="str">
-        <v>miriam.1969@hotmail.com</v>
+        <v>thaisaparecidamtz@hotmail.com</v>
       </c>
       <c r="C38" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D38" t="str">
-        <v>Contabilidade</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E38" t="str">
-        <v>70426368649</v>
+        <v>36840</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -1955,10 +1951,10 @@
         <v>Sim</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-05-13 19:29:47</v>
+        <v>2026-05-13 08:58:54</v>
       </c>
       <c r="L38" t="str">
-        <v>2026-05-14 15:10:42</v>
+        <v>2026-05-14 15:10:56</v>
       </c>
       <c r="M38" t="str">
         <v>2026-05-26 09:00:00</v>
@@ -1966,40 +1962,40 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Kelen Lourenço Silva Oliveira</v>
+        <v>Victor Hugo Pereira Reis</v>
       </c>
       <c r="B39" t="str">
-        <v>kelen.oliveira@pedroleopoldo.mg.gov.br</v>
+        <v>victor.reis@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C39" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D39" t="str">
-        <v>Coordenador de Assessoramento</v>
+        <v>Gerente de Infraestrutura de TIC</v>
       </c>
       <c r="E39" t="str">
-        <v>8113</v>
+        <v>9076</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H39" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I39" t="str">
         <v>Sim</v>
       </c>
       <c r="J39" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-05-14 09:06:56</v>
+        <v>2026-05-13 11:32:06</v>
       </c>
       <c r="L39" t="str">
-        <v/>
+        <v>2026-05-14 15:10:07</v>
       </c>
       <c r="M39" t="str">
         <v>2026-05-26 09:00:00</v>
